--- a/data/awards.xlsx
+++ b/data/awards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/conorisco/Dropbox (Personal)/Jobs/CV and Publications/CV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A72DFE-C091-4843-8E98-471303514891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF135DA4-374F-464D-8DCA-C1024077A50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1460" windowWidth="15600" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>with</t>
   </si>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>Valedictorian - Biochemistry with Immunology degree</t>
+  </si>
+  <si>
+    <t>Award for Excellence in Research Student Supervision 2025/26 (Nominated)</t>
   </si>
 </sst>
 </file>
@@ -440,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="47.6640625" customWidth="1"/>
@@ -561,6 +564,11 @@
         <v>2021</v>
       </c>
     </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
